--- a/KURIKULUM2026_REVISI/012_ANALISIS_KRITIS_JALUR_PONDASI_DAN_TREE_PRASYARAT.xlsx
+++ b/KURIKULUM2026_REVISI/012_ANALISIS_KRITIS_JALUR_PONDASI_DAN_TREE_PRASYARAT.xlsx
@@ -1097,7 +1097,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>`FST-408` Probstat, `FST-208` Stat Dasar</t>
+          <t>`FST-408` Probabilitas &amp; Statistika</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>`STI-301` APSI, `STI-205` Etika</t>
+          <t>`STI-301` APSI, `FST-206` Etika</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">

--- a/KURIKULUM2026_REVISI/012_ANALISIS_KRITIS_JALUR_PONDASI_DAN_TREE_PRASYARAT.xlsx
+++ b/KURIKULUM2026_REVISI/012_ANALISIS_KRITIS_JALUR_PONDASI_DAN_TREE_PRASYARAT.xlsx
@@ -568,12 +568,12 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>`STI-501`</t>
+          <t>`STI-519`</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Deep Learning &amp; Neural Networks</t>
+          <t>Keamanan Informasi Lanjut</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -583,17 +583,17 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>+P</t>
+          <t>Teori</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>`STI-401` Machine Learning</t>
+          <t>`STI-418` Dasar Keamanan</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>`STI-202` Aljabar Linear, `FST-408` Probstat</t>
+          <t>`STI-312` Jarkom, `STB-01` NetSec</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>`STI-503`</t>
+          <t>`STI-520`</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -630,12 +630,12 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>`STI-401` ML, `STI-402` DW/BI</t>
+          <t>`STI-413` ML, `STI-415` DW/BI</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>`FST-207` Basis Data, `STI-201` Matdis</t>
+          <t>`FST-207` Basis Data, `STI-204` Matdis</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>`STI-504`</t>
+          <t>`STI-521`</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>`STI-307` Jarkom, `STI-305` OS</t>
+          <t>`STI-312` Jarkom, `STI-310` OS</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>`STI-505`</t>
+          <t>`STI-522`</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>`STI-306` Front, `STI-407` Back</t>
+          <t>`STI-311` Front, `STI-416` Back</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>`STI-303` UI/UX Design &amp; Prototyping</t>
+          <t>`STI-308` UI/UX Design &amp; Prototyping</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>`STI-506`</t>
+          <t>`STI-523`</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>`STI-301` APSI, `STI-304` RPL</t>
+          <t>`STI-306` APSI, `STI-309` RPL</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>`STI-401` Machine Learning</t>
+          <t>`STI-413` Machine Learning</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>`FST-207` Basis Data, `STI-302` AI</t>
+          <t>`FST-207` Basis Data, `STI-307` AI</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -840,12 +840,12 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>`STI-307` Jarkom, `STI-405` Security</t>
+          <t>`STI-312` Jarkom, `STI-418` Security</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>`STI-305` Sistem Operasi</t>
+          <t>`STI-310` Sistem Operasi</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>`STI-303` UI/UX Design</t>
+          <t>`STI-308` UI/UX Design</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>`STI-306` Web Front-End</t>
+          <t>`STI-311` Web Front-End</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>`STI-601`</t>
+          <t>`STI-624`</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -924,12 +924,12 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>`STI-501` DL, `STI-407` Back End</t>
+          <t>`STI-413` ML, `STI-416` Back End</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>`STI-403` NLP &amp; IR, `STI-401` ML</t>
+          <t>`STI-414` NLP &amp; IR, `STI-307` Cerdas</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>`STI-602`</t>
+          <t>`STI-625`</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>`STI-504` IoT</t>
+          <t>`STI-521` IoT</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>`STI-301` APSI, `STI-404` Cloud</t>
+          <t>`STI-306` APSI, `STI-417` Cloud</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>`STI-603`</t>
+          <t>`STI-626`</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Keamanan Informasi Lanjut</t>
+          <t>Deep Learning &amp; Neural Networks</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Teori</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>`STI-405` Dasar Keamanan</t>
+          <t>`STI-413` Machine Learning</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>`STI-307` Jarkom, `STB-01` NetSec</t>
+          <t>`STI-205` Aljabar Linear, `FST-408` Probstat</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>`STI-604`</t>
+          <t>`STI-627`</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>`STI-407` Web Back End</t>
+          <t>`STI-416` Web Back End</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>`STI-404` Cloud, `STI-304` RPL</t>
+          <t>`STI-417` Cloud, `STI-309` RPL</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>`STI-202` Aljabar, `STI-102` Kalkulus</t>
+          <t>`STI-205` Aljabar, `STI-102` Kalkulus</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>`STI-302` AI, `STI-401` ML</t>
+          <t>`STI-307` AI, `STI-413` ML</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>`STI-201` Matdis (Graph &amp; Logic)</t>
+          <t>`STI-204` Matdis (Graph &amp; Logic)</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>`STI-404` Cloud Computing</t>
+          <t>`STI-417` Cloud Computing</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>`STI-305` OS, `STI-407` Web Back End</t>
+          <t>`STI-310` OS, `STI-416` Web Back End</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>`STI-405` Dasar Keamanan</t>
+          <t>`STI-418` Dasar Keamanan</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>`STI-307` Jarkom, `STB-01` NetSec</t>
+          <t>`STI-312` Jarkom, `STB-01` NetSec</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>`STI-301` APSI</t>
+          <t>`STI-306` APSI</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>`STI-304` Rekayasa Perangkat Lunak</t>
+          <t>`STI-309` Rekayasa Perangkat Lunak</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>`STI-407` Back End, `STI-306` Front</t>
+          <t>`STI-416` Back End, `STI-311` Front</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>`STI-505` Pemrograman Mobile</t>
+          <t>`STI-522` Pemrograman Mobile</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>`STI-701`</t>
+          <t>`STI-728`</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>`STI-604` Platform, `MKU-204` KWU</t>
+          <t>`STI-627` Platform, `MKU-204` KWU</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>`STI-506` Manajemen Proyek TI</t>
+          <t>`STI-523` Manajemen Proyek TI</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>`STI-506` Manpro, $\ge 100\text{ SKS}$</t>
+          <t>`STI-523` Manpro, $\ge 100\text{ SKS}$</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>`STI-501` DL, `STI-404` Cloud</t>
+          <t>`STI-626` DL, `STI-417` Cloud</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>`STA-01` DSS, `STI-401` ML</t>
+          <t>`STA-01` DSS, `STI-413` ML</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>`STI-403` NLP &amp; IR, `STI-501` DL</t>
+          <t>`STI-414` NLP &amp; IR, `STI-626` DL</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>`STI-601` Integrasi Layanan Cerdas AI</t>
+          <t>`STI-624` Integrasi Layanan Cerdas AI</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>`STI-501` DL, `STI-504` IoT</t>
+          <t>`STI-626` DL, `STI-521` IoT</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>`STI-401` Machine Learning</t>
+          <t>`STI-413` Machine Learning</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>`STI-301` APSI, `FST-206` Etika</t>
+          <t>`STI-306` APSI, `FST-206` Etika</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>`STI-506` Manajemen Proyek TI</t>
+          <t>`STI-523` Manajemen Proyek TI</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
@@ -1722,12 +1722,12 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>`STI-404` Cloud, `STI-603` Security</t>
+          <t>`STI-417` Cloud, `STI-519` Security</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>`STI-201` Matdis (Number Theory/Kripto)</t>
+          <t>`STI-204` Matdis (Number Theory/Kripto)</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>`STB-02` DevOps, `STI-404` Cloud</t>
+          <t>`STB-02` DevOps, `STI-417` Cloud</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>`STI-305` Sistem Operasi</t>
+          <t>`STI-310` Sistem Operasi</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>`STI-303` UI/UX, `STI-306` Front</t>
+          <t>`STI-308` UI/UX, `STI-311` Front</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -1848,12 +1848,12 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>`STI-604` Platform, `STI-404` Cloud</t>
+          <t>`STI-627` Platform, `STI-417` Cloud</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>`STI-407` Web Back End Development</t>
+          <t>`STI-416` Web Back End Development</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>`STI-701` Startup, `STI-303` UI/UX</t>
+          <t>`STI-728` Startup, `STI-308` UI/UX</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">

--- a/KURIKULUM2026_REVISI/012_ANALISIS_KRITIS_JALUR_PONDASI_DAN_TREE_PRASYARAT.xlsx
+++ b/KURIKULUM2026_REVISI/012_ANALISIS_KRITIS_JALUR_PONDASI_DAN_TREE_PRASYARAT.xlsx
@@ -593,7 +593,7 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>`STI-312` Jarkom, `STB-01` NetSec</t>
+          <t>`STI-312` Jarkom, `STB-501` NetSec</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
@@ -776,9 +776,9 @@
           <t>**5**</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>`STA-01`</t>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>`STA-501`</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -818,9 +818,9 @@
           <t>**5**</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>`STB-01`</t>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>`STB-501`</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -860,9 +860,9 @@
           <t>**5**</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>`STC-01`</t>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>`STC-501`</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -1112,9 +1112,9 @@
           <t>**6**</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>`STA-02`</t>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>`STA-601`</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -1154,9 +1154,9 @@
           <t>**6**</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>`STA-03`</t>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>`STA-602`</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -1196,9 +1196,9 @@
           <t>**6**</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>`STB-02`</t>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>`STB-601`</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1238,9 +1238,9 @@
           <t>**6**</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>`STB-03`</t>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>`STB-602`</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>`STI-312` Jarkom, `STB-01` NetSec</t>
+          <t>`STI-312` Jarkom, `STB-501` NetSec</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1280,9 +1280,9 @@
           <t>**6**</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>`STC-02`</t>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>`STC-601`</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1322,9 +1322,9 @@
           <t>**6**</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>`STC-03`</t>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>`STC-602`</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1532,9 +1532,9 @@
           <t>**7**</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>`STA-04`</t>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>`STA-701`</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>`STA-01` DSS, `STI-413` ML</t>
+          <t>`STA-501` DSS, `STI-413` ML</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
@@ -1574,9 +1574,9 @@
           <t>**7**</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>`STA-05`</t>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>`STA-702`</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -1616,9 +1616,9 @@
           <t>**7**</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>`STA-06`</t>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>`STA-703`</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -1658,9 +1658,9 @@
           <t>**7**</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>`STB-04`</t>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>`STB-701`</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -1700,9 +1700,9 @@
           <t>**7**</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>`STB-05`</t>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>`STB-702`</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -1742,9 +1742,9 @@
           <t>**7**</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>`STB-06`</t>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>`STB-703`</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>`STB-02` DevOps, `STI-417` Cloud</t>
+          <t>`STB-601` DevOps, `STI-417` Cloud</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -1784,9 +1784,9 @@
           <t>**7**</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>`STC-04`</t>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>`STC-701`</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
@@ -1826,9 +1826,9 @@
           <t>**7**</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>`STC-05`</t>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>`STC-702`</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -1868,9 +1868,9 @@
           <t>**7**</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>`STC-06`</t>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>`STC-703`</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
